--- a/scenarios/Coal_Flexibilisation/scenarios_to_run.xlsx
+++ b/scenarios/Coal_Flexibilisation/scenarios_to_run.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rlinstitutde-my.sharepoint.com/personal/agatha_majcher_rl-institut_de/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_D181A226D051B88EEA2B40D65E8A06BE8AC2DD14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD42B3ED-83CA-400F-9EB3-091D252566D7}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_D181A226D051B88EEA2B40D65E8A06BE8AC2DD14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E43DBF34-BC61-4F45-863C-045BC33B3EE1}"/>
   <bookViews>
-    <workbookView xWindow="8610" yWindow="-15795" windowWidth="17880" windowHeight="15465" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="735" windowWidth="17880" windowHeight="15465" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenario_definition" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="163">
   <si>
     <t>index</t>
   </si>
@@ -519,6 +519,9 @@
   </si>
   <si>
     <t>LOWDelEVs</t>
+  </si>
+  <si>
+    <t>LC-2190h</t>
   </si>
 </sst>
 </file>
@@ -777,6 +780,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1327,7 +1334,7 @@
         <v>52</v>
       </c>
       <c r="O2" s="19" t="s">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="P2" s="17" t="s">
         <v>54</v>
@@ -1466,7 +1473,7 @@
         <v>52</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="P3" s="17" t="s">
         <v>54</v>
@@ -1605,7 +1612,7 @@
         <v>52</v>
       </c>
       <c r="O4" s="19" t="s">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="P4" s="17" t="s">
         <v>54</v>
@@ -1744,7 +1751,7 @@
         <v>52</v>
       </c>
       <c r="O5" s="19" t="s">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="P5" s="17" t="s">
         <v>54</v>

--- a/scenarios/Coal_Flexibilisation/scenarios_to_run.xlsx
+++ b/scenarios/Coal_Flexibilisation/scenarios_to_run.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rlinstitutde-my.sharepoint.com/personal/agatha_majcher_rl-institut_de/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_D181A226D051B88EEA2B40D65E8A06BE8AC2DD14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E43DBF34-BC61-4F45-863C-045BC33B3EE1}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_D181A226D051B88EEA2B40D65E8A06BE8AC2DD14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4CA435D-B882-418A-B23D-419D6B93730A}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="735" windowWidth="17880" windowHeight="15465" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenario_definition" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="165">
   <si>
     <t>index</t>
   </si>
@@ -522,6 +522,12 @@
   </si>
   <si>
     <t>LC-2190h</t>
+  </si>
+  <si>
+    <t>co2_cap</t>
+  </si>
+  <si>
+    <t>* added! Sets a co2 emission cap (not run by carbon contraint (that is reinvestment)</t>
   </si>
 </sst>
 </file>
@@ -1103,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AS12"/>
+  <dimension ref="A1:AT12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" customWidth="1"/>
@@ -1145,13 +1151,13 @@
     <col min="39" max="39" width="8.7109375" style="3" customWidth="1"/>
     <col min="40" max="40" width="10" style="3" customWidth="1"/>
     <col min="41" max="41" width="13" style="3" customWidth="1"/>
-    <col min="42" max="42" width="8.42578125" style="3" customWidth="1"/>
-    <col min="43" max="43" width="15.5703125" style="3" customWidth="1"/>
-    <col min="44" max="44" width="15.42578125" style="3" customWidth="1"/>
-    <col min="45" max="45" width="15.85546875" style="3" customWidth="1"/>
+    <col min="42" max="43" width="8.42578125" style="3" customWidth="1"/>
+    <col min="44" max="44" width="15.5703125" style="3" customWidth="1"/>
+    <col min="45" max="45" width="15.42578125" style="3" customWidth="1"/>
+    <col min="46" max="46" width="15.85546875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" s="7" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" s="7" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1279,16 +1285,19 @@
         <v>41</v>
       </c>
       <c r="AQ1" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="AR1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="11" t="s">
+      <c r="AS1" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="11" t="s">
+      <c r="AT1" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:45" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
         <v>1</v>
       </c>
@@ -1417,17 +1426,20 @@
       <c r="AP2" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="AQ2" s="30" t="s">
+      <c r="AQ2" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR2" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="AR2" s="17" t="s">
+      <c r="AS2" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="AS2" s="17" t="s">
+      <c r="AT2" s="17" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:45" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <v>2</v>
       </c>
@@ -1556,17 +1568,20 @@
       <c r="AP3" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="AQ3" s="30" t="s">
+      <c r="AQ3" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR3" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="AR3" s="17" t="s">
+      <c r="AS3" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="AS3" s="17" t="s">
+      <c r="AT3" s="17" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:45" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <v>3</v>
       </c>
@@ -1695,17 +1710,20 @@
       <c r="AP4" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="AQ4" s="30" t="s">
+      <c r="AQ4" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR4" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="AR4" s="17" t="s">
+      <c r="AS4" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="AS4" s="17" t="s">
+      <c r="AT4" s="17" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:45" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>4</v>
       </c>
@@ -1834,17 +1852,20 @@
       <c r="AP5" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="AQ5" s="30" t="s">
+      <c r="AQ5" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR5" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="AR5" s="17" t="s">
+      <c r="AS5" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="AS5" s="17" t="s">
+      <c r="AT5" s="17" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:45" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="22">
         <v>5</v>
       </c>
@@ -1974,17 +1995,20 @@
       <c r="AP6" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="AQ6" s="23" t="s">
+      <c r="AQ6" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR6" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="AR6" s="23" t="s">
+      <c r="AS6" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="AS6" s="23" t="s">
+      <c r="AT6" s="23" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:45" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="22">
         <v>6</v>
       </c>
@@ -2114,17 +2138,20 @@
       <c r="AP7" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="AQ7" s="23" t="s">
+      <c r="AQ7" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR7" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="AR7" s="23" t="s">
+      <c r="AS7" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="AS7" s="23" t="s">
+      <c r="AT7" s="23" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:45" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="22">
         <v>7</v>
       </c>
@@ -2254,17 +2281,20 @@
       <c r="AP8" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="AQ8" s="23" t="s">
+      <c r="AQ8" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR8" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="AR8" s="23" t="s">
+      <c r="AS8" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="AS8" s="23" t="s">
+      <c r="AT8" s="23" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:45" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22">
         <v>8</v>
       </c>
@@ -2394,17 +2424,20 @@
       <c r="AP9" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="AQ9" s="23" t="s">
+      <c r="AQ9" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR9" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="AR9" s="23" t="s">
+      <c r="AS9" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="AS9" s="23" t="s">
+      <c r="AT9" s="23" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:45" s="7" customFormat="1" ht="270" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:46" s="7" customFormat="1" ht="270" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="27"/>
       <c r="C11" s="4" t="s">
@@ -2528,16 +2561,19 @@
         <v>116</v>
       </c>
       <c r="AQ11" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="AR11" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="AR11" s="4" t="s">
+      <c r="AS11" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="AS11" s="4" t="s">
+      <c r="AT11" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:45" ht="345" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:46" ht="345" x14ac:dyDescent="0.25">
       <c r="C12" s="4" t="s">
         <v>120</v>
       </c>
@@ -2658,13 +2694,14 @@
       <c r="AP12" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="AQ12" s="4" t="s">
+      <c r="AQ12" s="4"/>
+      <c r="AR12" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="AR12" s="4" t="s">
+      <c r="AS12" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="AS12" s="4" t="s">
+      <c r="AT12" s="4" t="s">
         <v>160</v>
       </c>
     </row>

--- a/scenarios/Coal_Flexibilisation/scenarios_to_run.xlsx
+++ b/scenarios/Coal_Flexibilisation/scenarios_to_run.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rlinstitutde-my.sharepoint.com/personal/agatha_majcher_rl-institut_de/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_D181A226D051B88EEA2B40D65E8A06BE8AC2DD14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4CA435D-B882-418A-B23D-419D6B93730A}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_D181A226D051B88EEA2B40D65E8A06BE8AC2DD14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13628CD3-7C61-4A9F-B974-853BBA9A6CD3}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="15" windowWidth="17880" windowHeight="15465" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenario_definition" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="164">
   <si>
     <t>index</t>
   </si>
@@ -519,9 +519,6 @@
   </si>
   <si>
     <t>LOWDelEVs</t>
-  </si>
-  <si>
-    <t>LC-2190h</t>
   </si>
   <si>
     <t>co2_cap</t>
@@ -1285,7 +1282,7 @@
         <v>41</v>
       </c>
       <c r="AQ1" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AR1" s="15" t="s">
         <v>42</v>
@@ -1343,7 +1340,7 @@
         <v>52</v>
       </c>
       <c r="O2" s="19" t="s">
-        <v>162</v>
+        <v>53</v>
       </c>
       <c r="P2" s="17" t="s">
         <v>54</v>
@@ -1485,7 +1482,7 @@
         <v>52</v>
       </c>
       <c r="O3" s="19" t="s">
-        <v>162</v>
+        <v>53</v>
       </c>
       <c r="P3" s="17" t="s">
         <v>54</v>
@@ -1627,7 +1624,7 @@
         <v>52</v>
       </c>
       <c r="O4" s="19" t="s">
-        <v>162</v>
+        <v>53</v>
       </c>
       <c r="P4" s="17" t="s">
         <v>54</v>
@@ -1769,7 +1766,7 @@
         <v>52</v>
       </c>
       <c r="O5" s="19" t="s">
-        <v>162</v>
+        <v>53</v>
       </c>
       <c r="P5" s="17" t="s">
         <v>54</v>
@@ -2561,7 +2558,7 @@
         <v>116</v>
       </c>
       <c r="AQ11" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AR11" s="4" t="s">
         <v>117</v>
